--- a/email_results.xlsx
+++ b/email_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD74EACD-756F-455A-AD43-4D98EF7AA13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6D1FD8-90F8-494D-8EA1-00366ADEF02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="156">
   <si>
     <t>公司名稱</t>
   </si>
@@ -145,15 +145,6 @@
     <t>info@petros.com.tw</t>
   </si>
   <si>
-    <t>欣肉時代股份有限公司</t>
-  </si>
-  <si>
-    <t>http://www.roubytham.com.tw/</t>
-  </si>
-  <si>
-    <t>aec31088a6fb4f6eafac028a91e1cf21@o769852.ingest.sentry.io</t>
-  </si>
-  <si>
     <t>尉登有限公司</t>
   </si>
   <si>
@@ -382,9 +373,6 @@
     <t>https://www.hitcatbrewing.com/</t>
   </si>
   <si>
-    <t>hitcat@fstshafts.com.tw, aec31088a6fb4f6eafac028a91e1cf21@o769852.ingest.sentry.io</t>
-  </si>
-  <si>
     <t>冰閣國際有限公司</t>
   </si>
   <si>
@@ -406,9 +394,6 @@
     <t>https://www.lasoffitta.com.tw</t>
   </si>
   <si>
-    <t>contact@support.com, service@lasoffitta.com.tw</t>
-  </si>
-  <si>
     <t>知淳興業股份有限公司</t>
   </si>
   <si>
@@ -497,6 +482,14 @@
   </si>
   <si>
     <t>contact@pigmentswine.com</t>
+  </si>
+  <si>
+    <t>hitcat@fstshafts.com.tw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>service@lasoffitta.com.tw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -561,11 +554,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -868,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
@@ -893,41 +887,41 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -935,13 +929,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -949,153 +943,153 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
+        <v>123</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
+        <v>116</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1103,13 +1097,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1117,55 +1111,55 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>152</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1173,41 +1167,41 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1215,27 +1209,27 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>151</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1243,27 +1237,27 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1271,27 +1265,27 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1299,10 +1293,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -1313,24 +1307,24 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>157</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -1341,108 +1335,108 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
@@ -1453,10 +1447,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
@@ -1467,10 +1461,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
@@ -1481,10 +1475,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
@@ -1495,38 +1489,38 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="B46" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -1537,38 +1531,38 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C50" t="s">
         <v>9</v>
@@ -1579,24 +1573,24 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="C52" t="s">
         <v>9</v>
@@ -1607,10 +1601,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="C53" t="s">
         <v>9</v>
@@ -1621,52 +1615,52 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="B54" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C54" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="D54">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C55" t="s">
-        <v>158</v>
+        <v>9</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="B56" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C56" t="s">
-        <v>140</v>
+        <v>9</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
@@ -1677,10 +1671,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
@@ -1691,10 +1685,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B59" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
@@ -1705,24 +1699,24 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B60" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C61" t="s">
         <v>9</v>
@@ -1733,10 +1727,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C62" t="s">
         <v>9</v>
@@ -1745,22 +1739,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>154</v>
-      </c>
-      <c r="B63" t="s">
-        <v>155</v>
-      </c>
-      <c r="C63" t="s">
-        <v>156</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D62">
+    <sortCondition ref="C2:C62"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/email_results.xlsx
+++ b/email_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6D1FD8-90F8-494D-8EA1-00366ADEF02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282A6D9A-7554-4509-B617-D20E33E7ABFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -496,6 +496,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -559,7 +562,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -862,16 +865,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
     <col min="2" max="2" width="26.125" customWidth="1"/>
     <col min="3" max="3" width="42.375" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -885,7 +889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>128</v>
       </c>
@@ -899,7 +903,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>117</v>
       </c>
@@ -913,7 +917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -927,7 +931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -940,8 +944,11 @@
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>110</v>
       </c>
@@ -954,8 +961,11 @@
       <c r="D6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -969,7 +979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -982,36 +992,42 @@
       <c r="D8">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>122</v>
       </c>
       <c r="B9" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>155</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>115</v>
       </c>
       <c r="B10" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>154</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>78</v>
       </c>
@@ -1024,8 +1040,11 @@
       <c r="D11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>84</v>
       </c>
@@ -1039,7 +1058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -1053,7 +1072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1066,8 +1085,11 @@
       <c r="D14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -1080,8 +1102,11 @@
       <c r="D15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1094,8 +1119,11 @@
       <c r="D16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1108,8 +1136,11 @@
       <c r="D17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1123,7 +1154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -1136,8 +1167,11 @@
       <c r="D19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -1150,8 +1184,11 @@
       <c r="D20">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="2">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1165,7 +1202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>81</v>
       </c>
@@ -1179,7 +1216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>96</v>
       </c>
@@ -1193,7 +1230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -1207,7 +1244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>149</v>
       </c>
@@ -1221,7 +1258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -1235,7 +1272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>107</v>
       </c>
@@ -1249,7 +1286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -1263,7 +1300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -1277,7 +1314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>142</v>
       </c>
@@ -1291,7 +1328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1305,7 +1342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>16</v>
       </c>
